--- a/Телефонная книга Толубай.xlsx
+++ b/Телефонная книга Толубай.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aliadm\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98D095E-DC2B-4B5B-94D3-297C973F57D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17954813-2BEC-4EBE-A695-62BB5A828D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{29AEACC4-9E86-4D62-9569-C3876BC2943D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="337">
   <si>
     <t>Отдел</t>
   </si>
@@ -62,9 +62,6 @@
     <t>email</t>
   </si>
   <si>
-    <t>ОИТ</t>
-  </si>
-  <si>
     <t>Корешкова Ирина Ивановна</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>oit@tolubaybank.kg</t>
   </si>
   <si>
-    <t>ОИБ</t>
-  </si>
-  <si>
     <t>Боярский Вадим Анатольевич</t>
   </si>
   <si>
@@ -131,9 +125,6 @@
     <t>Председатель КпР, Член СД</t>
   </si>
   <si>
-    <t>Члены правления ЗАО АКБ "Толубай"</t>
-  </si>
-  <si>
     <t>Чекошев Айбек Мелисканович</t>
   </si>
   <si>
@@ -173,9 +164,6 @@
     <t>Советник Правления</t>
   </si>
   <si>
-    <t>Служба Внутреннего Аудита</t>
-  </si>
-  <si>
     <t>Омукеева Чолпон Джумабековна</t>
   </si>
   <si>
@@ -197,9 +185,6 @@
     <t>Начальник СРМ</t>
   </si>
   <si>
-    <t>Служба Комплаенс Контроля</t>
-  </si>
-  <si>
     <t>Бейшембиева Алия Кубанычбековна</t>
   </si>
   <si>
@@ -275,9 +260,6 @@
     <t>Мл. специалист РКО юр. лиц</t>
   </si>
   <si>
-    <t>ф.906344</t>
-  </si>
-  <si>
     <t>Казначейство</t>
   </si>
   <si>
@@ -299,14 +281,782 @@
     <t>Гл. специалист</t>
   </si>
   <si>
-    <t>ф.391777</t>
+    <t>903-321</t>
+  </si>
+  <si>
+    <t>392-555</t>
+  </si>
+  <si>
+    <t>391-700</t>
+  </si>
+  <si>
+    <t>391-616</t>
+  </si>
+  <si>
+    <t>906-375</t>
+  </si>
+  <si>
+    <t>391-999</t>
+  </si>
+  <si>
+    <t>392-500</t>
+  </si>
+  <si>
+    <t>392-600</t>
+  </si>
+  <si>
+    <t>903-350</t>
+  </si>
+  <si>
+    <t>903-360</t>
+  </si>
+  <si>
+    <t>906-345</t>
+  </si>
+  <si>
+    <t>906-322</t>
+  </si>
+  <si>
+    <t>906-388</t>
+  </si>
+  <si>
+    <t>906-373</t>
+  </si>
+  <si>
+    <t>Члены правления</t>
+  </si>
+  <si>
+    <t>Служба Вн. Аудита</t>
+  </si>
+  <si>
+    <t>Служба Компл. Контроля</t>
+  </si>
+  <si>
+    <t>Кредитное управление</t>
+  </si>
+  <si>
+    <t>Бердалиев Улугбек Байбекович</t>
+  </si>
+  <si>
+    <t>Темирбек уулу Эрбол</t>
+  </si>
+  <si>
+    <t>Абдисаматов Баласагын</t>
+  </si>
+  <si>
+    <t>Бегалиев Ниязбек</t>
+  </si>
+  <si>
+    <t>Бектемиров Бакыт</t>
+  </si>
+  <si>
+    <t>Дюшеналиев Кыдык</t>
+  </si>
+  <si>
+    <t>Осмонов Бекбол</t>
+  </si>
+  <si>
+    <t>Начальник КУ</t>
+  </si>
+  <si>
+    <t>392-000</t>
+  </si>
+  <si>
+    <t>619, 650</t>
+  </si>
+  <si>
+    <t>391-800</t>
+  </si>
+  <si>
+    <t>Зам. начальника 2-ой отд. КУ</t>
+  </si>
+  <si>
+    <t>Зам. нач. КУ, Начальник 2-отд.</t>
+  </si>
+  <si>
+    <t>Зам. нач. КУ, Начальник 1-отд.</t>
+  </si>
+  <si>
+    <t>616, 650</t>
+  </si>
+  <si>
+    <t>Специалист 2-ого отд. КУ</t>
+  </si>
+  <si>
+    <t>Специалист 1-отд. КУ</t>
+  </si>
+  <si>
+    <t>392-444</t>
+  </si>
+  <si>
+    <t>Кред. Упр. ЭУ</t>
+  </si>
+  <si>
+    <t>Турдумалиев Улан</t>
+  </si>
+  <si>
+    <t>Токталиев Эржан</t>
+  </si>
+  <si>
+    <t>Шаршенбаев Айдар</t>
+  </si>
+  <si>
+    <t>Начальник ЭУ</t>
+  </si>
+  <si>
+    <t>Гл. специалист КАО ЭУ</t>
+  </si>
+  <si>
+    <t>Специалст КАО ЭУ</t>
+  </si>
+  <si>
+    <t>615, 650</t>
+  </si>
+  <si>
+    <t>906-311</t>
+  </si>
+  <si>
+    <t>Отдел Кред. Операций</t>
+  </si>
+  <si>
+    <t>Толобай уулу Галимжан</t>
+  </si>
+  <si>
+    <t>Акылбекова Бегайым</t>
+  </si>
+  <si>
+    <t>Начальник ОКО</t>
+  </si>
+  <si>
+    <t>Зам. начальника ОКО</t>
+  </si>
+  <si>
+    <t>392-111</t>
+  </si>
+  <si>
+    <t>Отдел Инф. Технлологий</t>
+  </si>
+  <si>
+    <t>Офицер Инф. Безоп.</t>
+  </si>
+  <si>
+    <t>618, 655</t>
+  </si>
+  <si>
+    <t>Сектор Тех. Поддержки</t>
+  </si>
+  <si>
+    <t>Солиев Нурсултан</t>
+  </si>
+  <si>
+    <t>Бактытбек улуу Бексултан</t>
+  </si>
+  <si>
+    <t>Гл. специалст СТП</t>
+  </si>
+  <si>
+    <t>Специалист СТП</t>
+  </si>
+  <si>
+    <t>Отдел Платежных Карт</t>
+  </si>
+  <si>
+    <t>Емельжанов Руслан</t>
+  </si>
+  <si>
+    <t>Токтоматова Камилла</t>
+  </si>
+  <si>
+    <t>Начальник ОПК</t>
+  </si>
+  <si>
+    <t>Мл. специалист ОПК</t>
+  </si>
+  <si>
+    <t>629, 659</t>
+  </si>
+  <si>
+    <t>ОУ РКО физ. Лиц</t>
+  </si>
+  <si>
+    <t>Карабаева Жыпаргуль</t>
+  </si>
+  <si>
+    <t>Начальник РКО физ. лиц</t>
+  </si>
+  <si>
+    <t>604, 659</t>
+  </si>
+  <si>
+    <t>Рысбекова Бермет</t>
+  </si>
+  <si>
+    <t>Жолдошбекова Кумушкан</t>
+  </si>
+  <si>
+    <t>Стажер РКО физ. лиц</t>
+  </si>
+  <si>
+    <t>Мл. специалист РКО физ. лиц</t>
+  </si>
+  <si>
+    <t>605, 659</t>
+  </si>
+  <si>
+    <t>392-525</t>
+  </si>
+  <si>
+    <t>906-370</t>
+  </si>
+  <si>
+    <t>906-340</t>
+  </si>
+  <si>
+    <t>Касса</t>
+  </si>
+  <si>
+    <t>Иманканова Разгуль Шерботоевна</t>
+  </si>
+  <si>
+    <t>Сырдыбаева Назира</t>
+  </si>
+  <si>
+    <t>Дженчороева Назгуль</t>
+  </si>
+  <si>
+    <t>Менеджер по касс. Контролю</t>
+  </si>
+  <si>
+    <t>Зав. кассой ОУ</t>
+  </si>
+  <si>
+    <t>Кассир высшей категории</t>
+  </si>
+  <si>
+    <t>Касса, Обменный пункт</t>
+  </si>
+  <si>
+    <t>Касса, Денежные переводы</t>
+  </si>
+  <si>
+    <t>Сарбагышова Динара</t>
+  </si>
+  <si>
+    <t>Сулайманова Жылдыз</t>
+  </si>
+  <si>
+    <t>392-100</t>
+  </si>
+  <si>
+    <t>392-333</t>
+  </si>
+  <si>
+    <t>Архив</t>
+  </si>
+  <si>
+    <t>Абдырахманова Чинара Женишевна</t>
+  </si>
+  <si>
+    <t>Гл. архивариус</t>
+  </si>
+  <si>
+    <t>906-374</t>
+  </si>
+  <si>
+    <t>Служба безопасности</t>
+  </si>
+  <si>
+    <t>Эстебесов Кенжебек Озгорушович</t>
+  </si>
+  <si>
+    <t>Зам начальника СБ</t>
+  </si>
+  <si>
+    <t>101, 102</t>
+  </si>
+  <si>
+    <t>392-300, 906-371</t>
+  </si>
+  <si>
+    <t>Адм.-Хоз. Отдел</t>
+  </si>
+  <si>
+    <t>Ипасов Аманбек Кутушович</t>
+  </si>
+  <si>
+    <t>Начальник АХО</t>
+  </si>
+  <si>
+    <t>Мамбетакунов Нурбек</t>
+  </si>
+  <si>
+    <t>Специалист АХО</t>
+  </si>
+  <si>
+    <t>Алиахунов Акматжан</t>
+  </si>
+  <si>
+    <t>Алыкулов Чынгыз</t>
+  </si>
+  <si>
+    <t>Электрик/спец АХО</t>
+  </si>
+  <si>
+    <t>Разнорабочий 1-й категории</t>
+  </si>
+  <si>
+    <t>391-938</t>
+  </si>
+  <si>
+    <t>Технический персонал</t>
+  </si>
+  <si>
+    <t>Абдуллаева Сабоат</t>
+  </si>
+  <si>
+    <t>Анарбаева Назира</t>
+  </si>
+  <si>
+    <t>Искендерова Назгул</t>
+  </si>
+  <si>
+    <t>Инзаркина Наталья</t>
+  </si>
+  <si>
+    <t>Тех. Персонал 1-ого этажа</t>
+  </si>
+  <si>
+    <t>Тех. Персонал 3-его этажа</t>
+  </si>
+  <si>
+    <t>Тех. Персонал 2-ого этажа</t>
+  </si>
+  <si>
+    <t>Столовая</t>
+  </si>
+  <si>
+    <t>Эльвира и Айзада</t>
+  </si>
+  <si>
+    <t>Повар и помощник</t>
+  </si>
+  <si>
+    <t>Водители банка</t>
+  </si>
+  <si>
+    <t>Мусаев Нурлан</t>
+  </si>
+  <si>
+    <t>Водитель-инкассатор</t>
+  </si>
+  <si>
+    <t>Джунушов Алмаз</t>
+  </si>
+  <si>
+    <t>Умуталиев Адыл</t>
+  </si>
+  <si>
+    <t>Мейманалиев Марлис</t>
+  </si>
+  <si>
+    <t>Толобаев Жайнак</t>
+  </si>
+  <si>
+    <t>Вавильченков Петр</t>
+  </si>
+  <si>
+    <t>Водитель</t>
+  </si>
+  <si>
+    <t>6596 ВС</t>
+  </si>
+  <si>
+    <t>6665 ВС</t>
+  </si>
+  <si>
+    <t>МВ 1090 ВВ</t>
+  </si>
+  <si>
+    <t>505 АК</t>
+  </si>
+  <si>
+    <t>МВ 1050 ВС</t>
+  </si>
+  <si>
+    <t>МВ 609 AD</t>
+  </si>
+  <si>
+    <t>Газета "Общ. рейтинг"</t>
+  </si>
+  <si>
+    <t>Рябкова Ольга Павловна</t>
+  </si>
+  <si>
+    <t>392-002</t>
+  </si>
+  <si>
+    <t>Отдел маркетинга</t>
+  </si>
+  <si>
+    <t>ОУЧР</t>
+  </si>
+  <si>
+    <t>Каб. Проверяющих</t>
+  </si>
+  <si>
+    <t>Хакимов Лутфулло</t>
+  </si>
+  <si>
+    <t>Маркетолог</t>
+  </si>
+  <si>
+    <t>Специалист ОУЧР</t>
+  </si>
+  <si>
+    <t>Программист</t>
+  </si>
+  <si>
+    <t>391-818</t>
+  </si>
+  <si>
+    <t>903-331</t>
+  </si>
+  <si>
+    <t>Бишкекский Филиал</t>
+  </si>
+  <si>
+    <t>Бекмурзаева Асель</t>
+  </si>
+  <si>
+    <t>Садырбаева Жаркынай</t>
+  </si>
+  <si>
+    <t>Мааразыкова Дамира</t>
+  </si>
+  <si>
+    <t>Директор БФ, Начальник КУ-1</t>
+  </si>
+  <si>
+    <t>Гл. специалист БФ</t>
+  </si>
+  <si>
+    <t>Техничка</t>
+  </si>
+  <si>
+    <t>590-232</t>
+  </si>
+  <si>
+    <t>591-428</t>
+  </si>
+  <si>
+    <t>ул. Л.Толсктого, 10; с 9:00 до 16:15</t>
+  </si>
+  <si>
+    <t>Суббота - с 10:00 до 12:30</t>
+  </si>
+  <si>
+    <t>ул. Киевская, 95А; с 8:45 до 16:15</t>
+  </si>
+  <si>
+    <t>Суббота - с 9:45 до 13:15</t>
+  </si>
+  <si>
+    <t>факс: 391-777</t>
+  </si>
+  <si>
+    <t>факс: 906-344</t>
+  </si>
+  <si>
+    <t>факс: 541-268</t>
+  </si>
+  <si>
+    <t>факс: 901-437</t>
+  </si>
+  <si>
+    <t>Гл. специалист СК-01</t>
+  </si>
+  <si>
+    <t>Сбер. Касса № 01</t>
+  </si>
+  <si>
+    <t>665-414</t>
+  </si>
+  <si>
+    <t>Шайхидинов Адиль</t>
+  </si>
+  <si>
+    <t>Мамырбекова Атыргуль Дженкулвна</t>
+  </si>
+  <si>
+    <t>Чегирткенова Гульнура Кенешовна</t>
+  </si>
+  <si>
+    <t>Алгожоева Шоола</t>
+  </si>
+  <si>
+    <t>Каныбекова Айым</t>
+  </si>
+  <si>
+    <t>Шамшиева Ырыс</t>
+  </si>
+  <si>
+    <t>Жакыпов Бекзат</t>
+  </si>
+  <si>
+    <t>Приемная банка (2-этаж)</t>
+  </si>
+  <si>
+    <t>Приемная банка (1-этаж)</t>
+  </si>
+  <si>
+    <t>Приемная банка (3-этаж)</t>
+  </si>
+  <si>
+    <t>Зам. админ. менеджера</t>
+  </si>
+  <si>
+    <t>Офис-менеджер</t>
+  </si>
+  <si>
+    <t>Старший офис-менеджер</t>
+  </si>
+  <si>
+    <t>Старший ассистент сов. СД</t>
+  </si>
+  <si>
+    <t>109, 199</t>
+  </si>
+  <si>
+    <t>392-392</t>
+  </si>
+  <si>
+    <t>факс: 902-902</t>
+  </si>
+  <si>
+    <t>Филиал "Толубай-Запад"</t>
+  </si>
+  <si>
+    <t>ул. Ахунбаева, 129; с 9:00 до 16:15</t>
+  </si>
+  <si>
+    <t>Суббота - с 10:00 до 13:15</t>
+  </si>
+  <si>
+    <t>Данияр к.Мадина</t>
+  </si>
+  <si>
+    <t>Усубакунова Жылдыз</t>
+  </si>
+  <si>
+    <t>Мищенко Наталья</t>
+  </si>
+  <si>
+    <t>Мл. специалист СК-03</t>
+  </si>
+  <si>
+    <t>565-284</t>
+  </si>
+  <si>
+    <t>566-687</t>
+  </si>
+  <si>
+    <t>Сбер. Касса № 04</t>
+  </si>
+  <si>
+    <t>Сбер. Касса № 05</t>
+  </si>
+  <si>
+    <t>Сбер. Касса № 06</t>
+  </si>
+  <si>
+    <t>sk3@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>Боркоев Шабданбек Калыбекович</t>
+  </si>
+  <si>
+    <t>Мамараимова Мээрим</t>
+  </si>
+  <si>
+    <t>Кудайбериева Венера</t>
+  </si>
+  <si>
+    <t>Ашималиева Алмаш</t>
+  </si>
+  <si>
+    <t>ЧП, Директор ФТЗ</t>
+  </si>
+  <si>
+    <t>Гл. специалист РКО ФТЗ</t>
+  </si>
+  <si>
+    <t>655-888, 651-119</t>
+  </si>
+  <si>
+    <t>341-668</t>
+  </si>
+  <si>
+    <t>факс: 343-280</t>
+  </si>
+  <si>
+    <t>Ст. специалист РКО ФТЗ</t>
+  </si>
+  <si>
+    <t>Специалист РКО ФТЗ</t>
+  </si>
+  <si>
+    <t>341-555</t>
+  </si>
+  <si>
+    <t>Ахунбаев Рустам</t>
+  </si>
+  <si>
+    <t>Боронбаев Анвар</t>
+  </si>
+  <si>
+    <t>Кадыркулова Жанара</t>
+  </si>
+  <si>
+    <t>Мааткеримова Динара</t>
+  </si>
+  <si>
+    <t>Кожоналиева Асылгуль</t>
+  </si>
+  <si>
+    <t>Кольдашева Бактыгуль</t>
+  </si>
+  <si>
+    <t>Садыкбеков Таалайбек</t>
+  </si>
+  <si>
+    <t>Зам. дир. ФТЗ, нач. КО ФТЗ</t>
+  </si>
+  <si>
+    <t>341-877</t>
+  </si>
+  <si>
+    <t>Специалист КО ФТЗ</t>
+  </si>
+  <si>
+    <t>655-951</t>
+  </si>
+  <si>
+    <t>Техничка ФТЗ</t>
+  </si>
+  <si>
+    <t>Разнорабочий 2-й категории</t>
+  </si>
+  <si>
+    <t>644-236</t>
+  </si>
+  <si>
+    <t>Ломбард "Дайым"</t>
+  </si>
+  <si>
+    <t>Биджанов Эдиль, Марат</t>
+  </si>
+  <si>
+    <t>656-220</t>
+  </si>
+  <si>
+    <t>654-877</t>
+  </si>
+  <si>
+    <t>Ломбард "Удача"</t>
+  </si>
+  <si>
+    <t>Vacant</t>
+  </si>
+  <si>
+    <t>Суббота - с 9:30 до 14:30</t>
+  </si>
+  <si>
+    <t>Редактор, но это не точно</t>
+  </si>
+  <si>
+    <t>Оценщик, но это не точно</t>
+  </si>
+  <si>
+    <t>ул. Токтогула 247, c 8:30 до 17:30</t>
+  </si>
+  <si>
+    <t>Сбер. Касса № 02</t>
+  </si>
+  <si>
+    <t>aho@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>assistent@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>auditext@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>diushenov@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>ftzko@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>hr@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>ib@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>jakypov_n@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>ku@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>nurbaiguttiev@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>oko@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>opk@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>ovo@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>piar@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>reception@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>sh.borkoev@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>skk@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>sva@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>tolobay.u.g@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>tolubay@banks.nbkr.kg</t>
+  </si>
+  <si>
+    <t>ubuio@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>uvoiocb@tolubaybank.kg</t>
+  </si>
+  <si>
+    <t>zhanaliev@tolubaybank.kg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,6 +1076,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="204"/>
@@ -694,7 +1451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69079538-E354-4416-BB63-8657EF42968E}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
@@ -729,13 +1486,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
         <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
       </c>
       <c r="D2">
         <v>444</v>
@@ -743,19 +1500,22 @@
       <c r="E2">
         <v>628</v>
       </c>
-      <c r="F2">
-        <v>903321</v>
+      <c r="F2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>405</v>
@@ -763,61 +1523,61 @@
       <c r="E3">
         <v>627</v>
       </c>
-      <c r="F3">
-        <v>392555</v>
+      <c r="F3" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>627</v>
       </c>
-      <c r="F4">
-        <v>392555</v>
+      <c r="F4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5">
-        <v>903321</v>
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>201</v>
@@ -825,152 +1585,164 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8">
-        <v>391700</v>
+      <c r="F8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E9">
         <v>620</v>
       </c>
-      <c r="F9">
-        <v>391616</v>
+      <c r="F9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D10">
         <v>245</v>
       </c>
-      <c r="F10">
-        <v>906375</v>
+      <c r="F10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D11">
         <v>212</v>
       </c>
-      <c r="F11">
-        <v>391999</v>
+      <c r="F11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D12">
         <v>342</v>
       </c>
-      <c r="F12">
-        <v>392500</v>
+      <c r="F12" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D13">
         <v>440</v>
       </c>
-      <c r="F13">
-        <v>392600</v>
+      <c r="F13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
         <v>44</v>
-      </c>
-      <c r="B14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
       </c>
       <c r="D14">
         <v>442</v>
       </c>
-      <c r="F14">
-        <v>392600</v>
+      <c r="F14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D15">
         <v>406</v>
       </c>
-      <c r="F15">
-        <v>903321</v>
+      <c r="F15" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D16">
         <v>340</v>
@@ -978,36 +1750,39 @@
       <c r="E16">
         <v>622</v>
       </c>
-      <c r="F16">
-        <v>903350</v>
+      <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D17">
         <v>345</v>
       </c>
-      <c r="F17">
-        <v>903350</v>
+      <c r="F17" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D18">
         <v>306</v>
@@ -1015,13 +1790,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D19">
         <v>227</v>
@@ -1029,19 +1804,19 @@
       <c r="E19">
         <v>614</v>
       </c>
-      <c r="F19">
-        <v>903360</v>
+      <c r="F19" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
         <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" t="s">
-        <v>63</v>
       </c>
       <c r="D20">
         <v>229</v>
@@ -1049,19 +1824,19 @@
       <c r="E20">
         <v>614</v>
       </c>
-      <c r="F20">
-        <v>903360</v>
+      <c r="F20" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D21">
         <v>228</v>
@@ -1072,13 +1847,13 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D22">
         <v>140</v>
@@ -1086,19 +1861,22 @@
       <c r="E22">
         <v>654</v>
       </c>
-      <c r="F22">
-        <v>906345</v>
+      <c r="F22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
         <v>65</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
       </c>
       <c r="D23">
         <v>131</v>
@@ -1106,19 +1884,22 @@
       <c r="E23">
         <v>654</v>
       </c>
-      <c r="F23">
-        <v>906375</v>
+      <c r="F23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D24">
         <v>240</v>
@@ -1126,16 +1907,19 @@
       <c r="E24">
         <v>654</v>
       </c>
+      <c r="G24" s="2" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D25">
         <v>132</v>
@@ -1143,19 +1927,19 @@
       <c r="E25">
         <v>656</v>
       </c>
-      <c r="F25">
-        <v>906322</v>
+      <c r="F25" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D26">
         <v>139</v>
@@ -1164,18 +1948,18 @@
         <v>656</v>
       </c>
       <c r="F26" t="s">
-        <v>78</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
         <v>72</v>
-      </c>
-      <c r="B27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" t="s">
-        <v>77</v>
       </c>
       <c r="D27">
         <v>138</v>
@@ -1183,53 +1967,59 @@
       <c r="E27">
         <v>656</v>
       </c>
-      <c r="F27">
-        <v>906388</v>
+      <c r="F27" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>39</v>
+      </c>
+      <c r="D28">
+        <v>212</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" t="s">
         <v>79</v>
       </c>
-      <c r="B29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
       <c r="D29">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E29">
         <v>652</v>
       </c>
-      <c r="F29">
-        <v>391999</v>
+      <c r="F29" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D30">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E30">
         <v>652</v>
@@ -1237,112 +2027,1438 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="E31">
         <v>652</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="D32">
-        <v>370</v>
+        <v>207</v>
       </c>
       <c r="E32">
-        <v>610</v>
-      </c>
-      <c r="F32">
-        <v>906373</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>10</v>
+        <v>650</v>
+      </c>
+      <c r="F32" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="D33">
-        <v>375</v>
-      </c>
-      <c r="E33">
-        <v>610</v>
-      </c>
-      <c r="F33">
-        <v>906373</v>
+        <v>208</v>
+      </c>
+      <c r="E33" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" t="s">
+        <v>106</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>13</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="D34">
-        <v>380</v>
-      </c>
-      <c r="E34">
-        <v>610</v>
-      </c>
-      <c r="F34">
-        <v>906373</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>15</v>
+        <v>208</v>
+      </c>
+      <c r="E34" t="s">
+        <v>107</v>
+      </c>
+      <c r="F34" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35">
+        <v>230</v>
+      </c>
+      <c r="E35" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36">
+        <v>220</v>
+      </c>
+      <c r="E36" t="s">
+        <v>107</v>
+      </c>
+      <c r="F36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37">
+        <v>223</v>
+      </c>
+      <c r="E37" t="s">
+        <v>112</v>
+      </c>
+      <c r="F37" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38">
+        <v>223</v>
+      </c>
+      <c r="E38" t="s">
+        <v>112</v>
+      </c>
+      <c r="F38" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39">
+        <v>233</v>
+      </c>
+      <c r="E39" t="s">
+        <v>123</v>
+      </c>
+      <c r="F39" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40">
+        <v>231</v>
+      </c>
+      <c r="E40" t="s">
+        <v>123</v>
+      </c>
+      <c r="F40" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D41">
+        <v>232</v>
+      </c>
+      <c r="E41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" t="s">
+        <v>126</v>
+      </c>
+      <c r="C42" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42">
+        <v>222</v>
+      </c>
+      <c r="F42" t="s">
+        <v>130</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43">
+        <v>234</v>
+      </c>
+      <c r="F43" t="s">
+        <v>130</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44">
+        <v>370</v>
+      </c>
+      <c r="E44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" t="s">
+        <v>93</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45">
+        <v>375</v>
+      </c>
+      <c r="E45" t="s">
+        <v>133</v>
+      </c>
+      <c r="F45" t="s">
+        <v>93</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46">
+        <v>380</v>
+      </c>
+      <c r="E46" t="s">
+        <v>133</v>
+      </c>
+      <c r="F46" t="s">
+        <v>93</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>132</v>
+      </c>
+      <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" t="s">
         <v>16</v>
       </c>
-      <c r="B35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35">
+      <c r="D47">
         <v>360</v>
       </c>
+      <c r="G47" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48" t="s">
+        <v>135</v>
+      </c>
+      <c r="C48" t="s">
+        <v>137</v>
+      </c>
+      <c r="D48">
+        <v>413</v>
+      </c>
+      <c r="E48">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" t="s">
+        <v>138</v>
+      </c>
+      <c r="D49">
+        <v>413</v>
+      </c>
+      <c r="E49">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" t="s">
+        <v>142</v>
+      </c>
+      <c r="D50">
+        <v>116</v>
+      </c>
+      <c r="E50">
+        <v>629</v>
+      </c>
+      <c r="F50" t="s">
+        <v>154</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" t="s">
+        <v>143</v>
+      </c>
+      <c r="D51">
+        <v>115</v>
+      </c>
+      <c r="E51" t="s">
+        <v>144</v>
+      </c>
+      <c r="F51" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" t="s">
+        <v>146</v>
+      </c>
+      <c r="C52" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52">
+        <v>120</v>
+      </c>
+      <c r="E52" t="s">
+        <v>148</v>
+      </c>
+      <c r="F52" t="s">
+        <v>155</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" t="s">
+        <v>152</v>
+      </c>
+      <c r="D53">
+        <v>124</v>
+      </c>
+      <c r="E53" t="s">
+        <v>153</v>
+      </c>
+      <c r="F53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>145</v>
+      </c>
+      <c r="B54" t="s">
+        <v>150</v>
+      </c>
+      <c r="C54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D54">
+        <v>121</v>
+      </c>
+      <c r="E54" t="s">
+        <v>148</v>
+      </c>
+      <c r="F54" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>157</v>
+      </c>
+      <c r="B55" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" t="s">
+        <v>161</v>
+      </c>
+      <c r="D55">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>157</v>
+      </c>
+      <c r="B56" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" t="s">
+        <v>162</v>
+      </c>
+      <c r="D56">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>157</v>
+      </c>
+      <c r="B57" t="s">
+        <v>160</v>
+      </c>
+      <c r="C57" t="s">
+        <v>163</v>
+      </c>
+      <c r="D57">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>164</v>
+      </c>
+      <c r="B58" t="s">
+        <v>166</v>
+      </c>
+      <c r="C58" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58">
+        <v>152</v>
+      </c>
+      <c r="F58" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>165</v>
+      </c>
+      <c r="B59" t="s">
+        <v>167</v>
+      </c>
+      <c r="C59" t="s">
+        <v>163</v>
+      </c>
+      <c r="D59">
+        <v>151</v>
+      </c>
+      <c r="F59" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>170</v>
+      </c>
+      <c r="B60" t="s">
+        <v>171</v>
+      </c>
+      <c r="C60" t="s">
+        <v>172</v>
+      </c>
+      <c r="D60">
+        <v>403</v>
+      </c>
+      <c r="F60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>174</v>
+      </c>
+      <c r="B61" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" t="s">
+        <v>176</v>
+      </c>
+      <c r="D61" t="s">
+        <v>177</v>
+      </c>
+      <c r="E61">
+        <v>610</v>
+      </c>
+      <c r="F61" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>179</v>
+      </c>
+      <c r="B62" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" t="s">
+        <v>181</v>
+      </c>
+      <c r="D62">
+        <v>404</v>
+      </c>
+      <c r="F62" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>179</v>
+      </c>
+      <c r="B63" t="s">
+        <v>182</v>
+      </c>
+      <c r="C63" t="s">
+        <v>183</v>
+      </c>
+      <c r="D63">
+        <v>411</v>
+      </c>
+      <c r="E63">
+        <v>630</v>
+      </c>
+      <c r="F63" t="s">
+        <v>188</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>179</v>
+      </c>
+      <c r="B64" t="s">
+        <v>184</v>
+      </c>
+      <c r="C64" t="s">
+        <v>186</v>
+      </c>
+      <c r="D64">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>179</v>
+      </c>
+      <c r="B65" t="s">
+        <v>185</v>
+      </c>
+      <c r="C65" t="s">
+        <v>187</v>
+      </c>
+      <c r="D65">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" t="s">
+        <v>190</v>
+      </c>
+      <c r="C66" t="s">
+        <v>194</v>
+      </c>
+      <c r="D66">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67" t="s">
+        <v>191</v>
+      </c>
+      <c r="C67" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" t="s">
+        <v>192</v>
+      </c>
+      <c r="C68" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>189</v>
+      </c>
+      <c r="B69" t="s">
+        <v>193</v>
+      </c>
+      <c r="C69" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>197</v>
+      </c>
+      <c r="B70" t="s">
+        <v>198</v>
+      </c>
+      <c r="C70" t="s">
+        <v>199</v>
+      </c>
+      <c r="D70">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>200</v>
+      </c>
+      <c r="B71" t="s">
+        <v>201</v>
+      </c>
+      <c r="C71" t="s">
+        <v>202</v>
+      </c>
+      <c r="D71">
+        <v>706</v>
+      </c>
+      <c r="F71" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>200</v>
+      </c>
+      <c r="B72" t="s">
+        <v>203</v>
+      </c>
+      <c r="C72" t="s">
+        <v>202</v>
+      </c>
+      <c r="D72">
+        <v>706</v>
+      </c>
+      <c r="F72" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>200</v>
+      </c>
+      <c r="B73" t="s">
+        <v>204</v>
+      </c>
+      <c r="C73" t="s">
+        <v>208</v>
+      </c>
+      <c r="D73">
+        <v>706</v>
+      </c>
+      <c r="F73" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>200</v>
+      </c>
+      <c r="B74" t="s">
+        <v>205</v>
+      </c>
+      <c r="C74" t="s">
+        <v>208</v>
+      </c>
+      <c r="D74">
+        <v>706</v>
+      </c>
+      <c r="F74" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>200</v>
+      </c>
+      <c r="B75" t="s">
+        <v>206</v>
+      </c>
+      <c r="C75" t="s">
+        <v>208</v>
+      </c>
+      <c r="D75">
+        <v>706</v>
+      </c>
+      <c r="F75" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>200</v>
+      </c>
+      <c r="B76" t="s">
+        <v>207</v>
+      </c>
+      <c r="C76" t="s">
+        <v>208</v>
+      </c>
+      <c r="D76">
+        <v>706</v>
+      </c>
+      <c r="F76" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>215</v>
+      </c>
+      <c r="B77" t="s">
+        <v>216</v>
+      </c>
+      <c r="C77" t="s">
+        <v>310</v>
+      </c>
+      <c r="D77">
+        <v>417</v>
+      </c>
+      <c r="F77" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>218</v>
+      </c>
+      <c r="B78" t="s">
+        <v>308</v>
+      </c>
+      <c r="C78" t="s">
+        <v>222</v>
+      </c>
+      <c r="D78">
+        <v>322</v>
+      </c>
+      <c r="F78" t="s">
+        <v>225</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>219</v>
+      </c>
+      <c r="B79" t="s">
+        <v>308</v>
+      </c>
+      <c r="C79" t="s">
+        <v>223</v>
+      </c>
+      <c r="D79">
+        <v>401</v>
+      </c>
+      <c r="F79" t="s">
+        <v>173</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>220</v>
+      </c>
+      <c r="B80" t="s">
+        <v>221</v>
+      </c>
+      <c r="C80" t="s">
+        <v>224</v>
+      </c>
+      <c r="D80">
+        <v>416</v>
+      </c>
+      <c r="F80" t="s">
+        <v>226</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>227</v>
+      </c>
+      <c r="B81" t="s">
+        <v>236</v>
+      </c>
+      <c r="C81" t="s">
+        <v>237</v>
+      </c>
+      <c r="F81" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>227</v>
+      </c>
+      <c r="B82" t="s">
+        <v>98</v>
+      </c>
+      <c r="C82" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>227</v>
+      </c>
+      <c r="B83" t="s">
+        <v>228</v>
+      </c>
+      <c r="C83" t="s">
+        <v>232</v>
+      </c>
+      <c r="F83" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>227</v>
+      </c>
+      <c r="B84" t="s">
+        <v>229</v>
+      </c>
+      <c r="C84" t="s">
+        <v>163</v>
+      </c>
+      <c r="F84" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>227</v>
+      </c>
+      <c r="B85" t="s">
+        <v>230</v>
+      </c>
+      <c r="C85" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>245</v>
+      </c>
+      <c r="B86" t="s">
+        <v>238</v>
+      </c>
+      <c r="C86" t="s">
+        <v>239</v>
+      </c>
+      <c r="E86">
+        <v>720001</v>
+      </c>
+      <c r="F86" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>245</v>
+      </c>
+      <c r="B87" t="s">
+        <v>228</v>
+      </c>
+      <c r="C87" t="s">
+        <v>244</v>
+      </c>
+      <c r="F87" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>254</v>
+      </c>
+      <c r="B88" t="s">
+        <v>247</v>
+      </c>
+      <c r="C88" t="s">
+        <v>257</v>
+      </c>
+      <c r="D88" t="s">
+        <v>30</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>254</v>
+      </c>
+      <c r="B89" t="s">
+        <v>248</v>
+      </c>
+      <c r="C89" t="s">
+        <v>258</v>
+      </c>
+      <c r="D89" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>255</v>
+      </c>
+      <c r="B90" t="s">
+        <v>249</v>
+      </c>
+      <c r="C90" t="s">
+        <v>259</v>
+      </c>
+      <c r="D90" t="s">
+        <v>261</v>
+      </c>
+      <c r="E90">
+        <v>602</v>
+      </c>
+      <c r="F90" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>255</v>
+      </c>
+      <c r="B91" t="s">
+        <v>250</v>
+      </c>
+      <c r="C91" t="s">
+        <v>258</v>
+      </c>
+      <c r="D91" t="s">
+        <v>261</v>
+      </c>
+      <c r="E91">
+        <v>602</v>
+      </c>
+      <c r="F91" t="s">
+        <v>263</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>255</v>
+      </c>
+      <c r="B92" t="s">
+        <v>251</v>
+      </c>
+      <c r="C92" t="s">
+        <v>258</v>
+      </c>
+      <c r="D92" t="s">
+        <v>261</v>
+      </c>
+      <c r="E92">
+        <v>602</v>
+      </c>
+      <c r="F92" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>255</v>
+      </c>
+      <c r="B93" t="s">
+        <v>252</v>
+      </c>
+      <c r="C93" t="s">
+        <v>258</v>
+      </c>
+      <c r="D93" t="s">
+        <v>261</v>
+      </c>
+      <c r="E93">
+        <v>602</v>
+      </c>
+      <c r="F93" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>256</v>
+      </c>
+      <c r="B94" t="s">
+        <v>253</v>
+      </c>
+      <c r="C94" t="s">
+        <v>260</v>
+      </c>
+      <c r="D94">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>313</v>
+      </c>
+      <c r="B95" t="s">
+        <v>265</v>
+      </c>
+      <c r="C95" t="s">
+        <v>266</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>273</v>
+      </c>
+      <c r="B96" t="s">
+        <v>267</v>
+      </c>
+      <c r="C96" t="s">
+        <v>270</v>
+      </c>
+      <c r="F96" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>274</v>
+      </c>
+      <c r="B97" t="s">
+        <v>268</v>
+      </c>
+      <c r="C97" t="s">
+        <v>163</v>
+      </c>
+      <c r="F97" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>275</v>
+      </c>
+      <c r="B98" t="s">
+        <v>269</v>
+      </c>
+      <c r="C98" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>264</v>
+      </c>
+      <c r="B99" t="s">
+        <v>312</v>
+      </c>
+      <c r="C99" t="s">
+        <v>309</v>
+      </c>
+      <c r="F99" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>264</v>
+      </c>
+      <c r="B100" t="s">
+        <v>277</v>
+      </c>
+      <c r="C100" t="s">
+        <v>281</v>
+      </c>
+      <c r="D100">
+        <v>106</v>
+      </c>
+      <c r="F100" t="s">
+        <v>283</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>264</v>
+      </c>
+      <c r="B101" t="s">
+        <v>278</v>
+      </c>
+      <c r="C101" t="s">
+        <v>282</v>
+      </c>
+      <c r="D101">
+        <v>125</v>
+      </c>
+      <c r="F101" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>264</v>
+      </c>
+      <c r="B102" t="s">
+        <v>279</v>
+      </c>
+      <c r="C102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D102">
+        <v>126</v>
+      </c>
+      <c r="F102" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>264</v>
+      </c>
+      <c r="B103" t="s">
+        <v>280</v>
+      </c>
+      <c r="C103" t="s">
+        <v>287</v>
+      </c>
+      <c r="D103">
+        <v>128</v>
+      </c>
+      <c r="F103" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>264</v>
+      </c>
+      <c r="B104" t="s">
+        <v>289</v>
+      </c>
+      <c r="C104" t="s">
+        <v>296</v>
+      </c>
+      <c r="D104">
+        <v>121</v>
+      </c>
+      <c r="F104" t="s">
+        <v>297</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>264</v>
+      </c>
+      <c r="B105" t="s">
+        <v>290</v>
+      </c>
+      <c r="C105" t="s">
+        <v>298</v>
+      </c>
+      <c r="D105">
+        <v>121</v>
+      </c>
+      <c r="F105" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>264</v>
+      </c>
+      <c r="B106" t="s">
+        <v>291</v>
+      </c>
+      <c r="C106" t="s">
+        <v>298</v>
+      </c>
+      <c r="D106">
+        <v>121</v>
+      </c>
+      <c r="F106" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>264</v>
+      </c>
+      <c r="B107" t="s">
+        <v>292</v>
+      </c>
+      <c r="C107" t="s">
+        <v>163</v>
+      </c>
+      <c r="D107">
+        <v>113</v>
+      </c>
+      <c r="F107" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>264</v>
+      </c>
+      <c r="B108" t="s">
+        <v>293</v>
+      </c>
+      <c r="C108" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>264</v>
+      </c>
+      <c r="B109" t="s">
+        <v>294</v>
+      </c>
+      <c r="C109" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>264</v>
+      </c>
+      <c r="B110" t="s">
+        <v>295</v>
+      </c>
+      <c r="C110" t="s">
+        <v>301</v>
+      </c>
+      <c r="F110" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>303</v>
+      </c>
+      <c r="B111" t="s">
+        <v>304</v>
+      </c>
+      <c r="C111" t="s">
+        <v>311</v>
+      </c>
+      <c r="F111" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>307</v>
+      </c>
+      <c r="B112" t="s">
+        <v>308</v>
+      </c>
+      <c r="C112" t="s">
+        <v>308</v>
+      </c>
+      <c r="F112" t="s">
+        <v>306</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G32" r:id="rId1" xr:uid="{4F97F874-EE61-4DE3-B6DE-AC25B734B64E}"/>
-    <hyperlink ref="G33" r:id="rId2" xr:uid="{8A6AD781-6DAB-4FD4-865B-E4C73C548BE3}"/>
-    <hyperlink ref="G34" r:id="rId3" xr:uid="{20FD8B55-FDC2-4F08-B643-FBDCDAB6C52D}"/>
+    <hyperlink ref="G44" r:id="rId1" xr:uid="{4F97F874-EE61-4DE3-B6DE-AC25B734B64E}"/>
+    <hyperlink ref="G45" r:id="rId2" xr:uid="{8A6AD781-6DAB-4FD4-865B-E4C73C548BE3}"/>
+    <hyperlink ref="G46" r:id="rId3" xr:uid="{20FD8B55-FDC2-4F08-B643-FBDCDAB6C52D}"/>
+    <hyperlink ref="G95" r:id="rId4" xr:uid="{00715C86-E2A4-470E-A679-6BD6F51CB35B}"/>
+    <hyperlink ref="G63" r:id="rId5" xr:uid="{38866A06-5114-4EF2-9E6B-B68070D3350B}"/>
+    <hyperlink ref="G88" r:id="rId6" xr:uid="{0171182E-A8CE-4866-BF69-A64854A9F756}"/>
+    <hyperlink ref="G80" r:id="rId7" xr:uid="{8A29A59B-25A5-442E-B82A-3ED334AD283F}"/>
+    <hyperlink ref="G2" r:id="rId8" xr:uid="{BFB74E01-F82D-48E0-86F2-6E08831313A0}"/>
+    <hyperlink ref="G104" r:id="rId9" xr:uid="{82117530-7B6D-4F13-B52B-5CDBED819A11}"/>
+    <hyperlink ref="G79" r:id="rId10" xr:uid="{4C8D7016-7D0A-4B49-8F9E-87EFC94B1E6A}"/>
+    <hyperlink ref="G47" r:id="rId11" xr:uid="{BED9A312-5B42-4868-BE8E-1FDDF435A741}"/>
+    <hyperlink ref="G22" r:id="rId12" xr:uid="{FB06A48A-4060-42E0-89AA-1F261A65AA30}"/>
+    <hyperlink ref="G33" r:id="rId13" xr:uid="{CE064772-5DE1-4B64-997F-A4480D54B800}"/>
+    <hyperlink ref="G50" r:id="rId14" xr:uid="{05E74155-019B-4F37-913C-A4B1A759C69E}"/>
+    <hyperlink ref="G52" r:id="rId15" xr:uid="{0C82835F-FD4B-4F71-BB3F-3151720C98E5}"/>
+    <hyperlink ref="G78" r:id="rId16" xr:uid="{2C32664C-326D-47C7-BD17-B01C538E9FD4}"/>
+    <hyperlink ref="G91" r:id="rId17" xr:uid="{0340907F-4F23-48B6-81C3-E85EADBE25AD}"/>
+    <hyperlink ref="G100" r:id="rId18" xr:uid="{101D0037-9524-474C-B82E-A61B78927571}"/>
+    <hyperlink ref="G16" r:id="rId19" xr:uid="{AB93D77D-0068-467B-875D-B152F729A1D7}"/>
+    <hyperlink ref="G13" r:id="rId20" xr:uid="{8AF52269-054F-4C15-A930-09CFC7F43DBF}"/>
+    <hyperlink ref="G14" r:id="rId21" xr:uid="{AC46B342-6363-4925-B8FC-553CD4740E2B}"/>
+    <hyperlink ref="G43" r:id="rId22" xr:uid="{76EE105D-9C06-4141-9153-3B28670182B4}"/>
+    <hyperlink ref="G42" r:id="rId23" xr:uid="{754E0185-FC2F-4BDC-9E5B-0319EF0D2EAE}"/>
+    <hyperlink ref="G23" r:id="rId24" xr:uid="{56692C5B-E671-40FA-A0E9-BEEE77074CEE}"/>
+    <hyperlink ref="G24" r:id="rId25" xr:uid="{252B7E60-BC46-45A2-ACDF-D55059BFE487}"/>
+    <hyperlink ref="G28" r:id="rId26" xr:uid="{0E1FA5DC-10D1-489C-A95A-6CCD1EDE2D90}"/>
+    <hyperlink ref="G11" r:id="rId27" xr:uid="{38A6DEB8-AC5E-4592-92EB-E3E6C593844E}"/>
+    <hyperlink ref="G9" r:id="rId28" xr:uid="{CD364CBC-3E43-4CB5-AD57-2AFDBBB0F06E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
